--- a/base.xlsx
+++ b/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.yuldashev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6CC10C3-A1E5-4EFE-A149-3FFB5F821645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8BDB5B-CA8B-4190-B400-28FBDF0C41F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4755" yWindow="0" windowWidth="18360" windowHeight="15195" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
@@ -1137,19 +1137,19 @@
     <t>B1F-7</t>
   </si>
   <si>
-    <t>Позиция (A)</t>
-  </si>
-  <si>
-    <t>РУ (B)</t>
-  </si>
-  <si>
-    <t>Ячейка (C)</t>
-  </si>
-  <si>
-    <t>Фидер (D)</t>
-  </si>
-  <si>
-    <t>Тип схемы (E)</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
   </si>
 </sst>
 </file>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.yuldashev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F8BDB5B-CA8B-4190-B400-28FBDF0C41F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867AD7C5-032E-403D-B579-B24DFB36465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4755" yWindow="0" windowWidth="18360" windowHeight="15195" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
+    <workbookView xWindow="270" yWindow="0" windowWidth="18360" windowHeight="15195" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
     <sheet name="A80-MSS-PC-100" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'A80-MSS-PC-100'!$A$1:$H$139</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'A80-MSS-PC-100'!$A$1:$E$139</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="371">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -1567,2799 +1567,2377 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
-    <col min="2" max="2" width="72.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" style="6" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="7.42578125" style="6" hidden="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" style="6" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="19.7109375" style="6" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="7" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" style="6" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>366</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>367</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>368</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>369</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="3" t="s">
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="3" t="s">
+      <c r="C4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="C5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="C6" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="C7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="3" t="s">
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="3" t="s">
+      <c r="C9" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="3" t="s">
+      <c r="C10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="3" t="s">
+      <c r="C11" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E11" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="3" t="s">
+      <c r="C12" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="H13" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E13" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="3" t="s">
+      <c r="C14" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="C15" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="C16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E16" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G17" s="3" t="s">
+      <c r="C17" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>40</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="3" t="s">
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="3" t="s">
+      <c r="C19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="H19" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E19" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="3" t="s">
+      <c r="C20" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="3" t="s">
+      <c r="C21" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="3" t="s">
+      <c r="C22" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G23" s="3" t="s">
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>55</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G24" s="3" t="s">
+      <c r="C24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="H24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>58</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="3" t="s">
+      <c r="C25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="H25" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E25" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="C26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G27" s="3" t="s">
+      <c r="C27" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>67</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="E28" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>71</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="3" t="s">
+      <c r="C29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D29" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="E29" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>74</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="3" t="s">
+      <c r="C30" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D30" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H30" s="3" t="s">
+      <c r="E30" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>76</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="3" t="s">
+      <c r="C31" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D31" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H31" s="3" t="s">
+      <c r="E31" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>78</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G32" s="3" t="s">
+      <c r="C32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="H32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="3" t="s">
+      <c r="C33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>83</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="3" t="s">
+      <c r="C34" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>87</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="3" t="s">
+      <c r="C35" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H35" s="3" t="s">
+      <c r="E35" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>90</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="3" t="s">
+      <c r="C36" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="H36" s="3" t="s">
+      <c r="E36" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>93</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="3" t="s">
+      <c r="C37" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H37" s="3" t="s">
+      <c r="E37" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>96</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="3" t="s">
+      <c r="C38" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H38" s="3" t="s">
+      <c r="E38" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>99</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="3" t="s">
+      <c r="C39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="H39" s="3" t="s">
+      <c r="E39" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>102</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="3" t="s">
+      <c r="C40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="H40" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E40" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>105</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G41" s="3" t="s">
+      <c r="C41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H41" s="3" t="s">
+      <c r="E41" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>108</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="3" t="s">
+      <c r="C42" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H42" s="3" t="s">
+      <c r="E42" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>111</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" s="3" t="s">
+      <c r="C43" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>114</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G44" s="3" t="s">
+      <c r="C44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="E44" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G45" s="3" t="s">
+      <c r="C45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D45" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H45" s="3" t="s">
+      <c r="E45" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>120</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="3" t="s">
+      <c r="C46" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D46" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H46" s="3" t="s">
+      <c r="E46" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>123</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="3" t="s">
+      <c r="C47" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="E47" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>125</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="3" t="s">
+      <c r="C48" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H48" s="3" t="s">
+      <c r="E48" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>129</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G49" s="3" t="s">
+      <c r="C49" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>132</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="3" t="s">
+      <c r="C50" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>135</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G51" s="3" t="s">
+      <c r="C51" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>138</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="3" t="s">
+      <c r="C52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>142</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G53" s="3" t="s">
+      <c r="C53" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>144</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G54" s="3" t="s">
+      <c r="C54" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>147</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G55" s="3" t="s">
+      <c r="C55" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>149</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G56" s="3" t="s">
+      <c r="C56" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G57" s="3" t="s">
+      <c r="C57" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>155</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G58" s="3" t="s">
+      <c r="C58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="E58" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>158</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G59" s="3" t="s">
+      <c r="C59" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="H59" s="3" t="s">
+      <c r="E59" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>161</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G60" s="3" t="s">
+      <c r="C60" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="E60" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>164</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G61" s="3" t="s">
+      <c r="C61" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G62" s="3" t="s">
+      <c r="C62" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="E62" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>170</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G63" s="3" t="s">
+      <c r="C63" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>173</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G64" s="3" t="s">
+      <c r="C64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="H64" s="3" t="s">
+      <c r="E64" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>176</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G65" s="3" t="s">
+      <c r="C65" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="H65" s="3" t="s">
+      <c r="E65" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>179</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G66" s="3" t="s">
+      <c r="C66" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="E66" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>182</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G67" s="3" t="s">
+      <c r="C67" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>185</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G68" s="3" t="s">
+      <c r="C68" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H68" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E68" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>188</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G69" s="3" t="s">
+      <c r="C69" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="H69" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E69" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>191</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G70" s="3" t="s">
+      <c r="C70" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>194</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G71" s="3" t="s">
+      <c r="C71" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="H71" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E71" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>197</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G72" s="3" t="s">
+      <c r="C72" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>200</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G73" s="3" t="s">
+      <c r="C73" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="E73" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>203</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C74" s="1"/>
-      <c r="D74" s="1"/>
-      <c r="E74" s="1"/>
-      <c r="F74" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G74" s="3" t="s">
+      <c r="C74" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="H74" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E74" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>206</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C75" s="1"/>
-      <c r="D75" s="1"/>
-      <c r="E75" s="1"/>
-      <c r="F75" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G75" s="3" t="s">
+      <c r="C75" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="H75" s="3" t="str">
-        <f>$H$65</f>
+      <c r="E75" s="3" t="str">
+        <f>$E$65</f>
         <v>LF-02A</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>209</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C76" s="1"/>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G76" s="3" t="s">
+      <c r="C76" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C77" s="1"/>
-      <c r="D77" s="1"/>
-      <c r="E77" s="1"/>
-      <c r="F77" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G77" s="3" t="s">
+      <c r="C77" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="H77" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E77" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>215</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C78" s="1"/>
-      <c r="D78" s="1"/>
-      <c r="E78" s="1"/>
-      <c r="F78" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G78" s="3" t="s">
+      <c r="C78" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="H78" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E78" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>217</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C79" s="1"/>
-      <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G79" s="3" t="s">
+      <c r="C79" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="H79" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E79" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>219</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="1"/>
-      <c r="D80" s="1"/>
-      <c r="E80" s="1"/>
-      <c r="F80" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G80" s="3" t="s">
+      <c r="C80" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="H80" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E80" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>219</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G81" s="3" t="s">
+      <c r="C81" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>222</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C82" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G82" s="3" t="s">
+      <c r="C82" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="H82" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E82" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>222</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G83" s="3" t="s">
+      <c r="C83" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>225</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C84" s="1"/>
-      <c r="D84" s="1"/>
-      <c r="E84" s="1"/>
-      <c r="F84" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G84" s="3" t="s">
+      <c r="C84" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="H84" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E84" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>225</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="1"/>
-      <c r="D85" s="1"/>
-      <c r="E85" s="1"/>
-      <c r="F85" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G85" s="3" t="s">
+      <c r="C85" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="H85" s="3" t="s">
+      <c r="E85" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>230</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C86" s="1"/>
-      <c r="D86" s="1"/>
-      <c r="E86" s="1"/>
-      <c r="F86" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G86" s="3" t="s">
+      <c r="C86" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D86" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="H86" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E86" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>232</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G87" s="3" t="s">
+      <c r="C87" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D87" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="H87" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E87" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>234</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C88" s="1"/>
-      <c r="D88" s="1"/>
-      <c r="E88" s="1"/>
-      <c r="F88" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G88" s="3" t="s">
+      <c r="C88" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="H88" s="3" t="s">
+      <c r="E88" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C89" s="1"/>
-      <c r="D89" s="1"/>
-      <c r="E89" s="1"/>
-      <c r="F89" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G89" s="3" t="s">
+      <c r="C89" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="H89" s="3" t="s">
+      <c r="E89" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>238</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C90" s="1"/>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G90" s="3" t="s">
+      <c r="C90" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D90" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="H90" s="3" t="s">
+      <c r="E90" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>240</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G91" s="3" t="s">
+      <c r="C91" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D91" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="H91" s="3" t="s">
+      <c r="E91" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>242</v>
       </c>
       <c r="B92" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G92" s="3" t="s">
+      <c r="C92" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D92" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="H92" s="3" t="s">
+      <c r="E92" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>245</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G93" s="3" t="s">
+      <c r="C93" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D93" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="H93" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E93" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>247</v>
       </c>
       <c r="B94" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G94" s="3" t="s">
+      <c r="C94" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D94" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>249</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G95" s="3" t="s">
+      <c r="C95" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="H95" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E95" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>251</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G96" s="3" t="s">
+      <c r="C96" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D96" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>251</v>
       </c>
       <c r="B97" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G97" s="3" t="s">
+      <c r="C97" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D97" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="H97" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E97" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>253</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C98" s="1"/>
-      <c r="D98" s="1"/>
-      <c r="E98" s="1"/>
-      <c r="F98" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G98" s="3" t="s">
+      <c r="C98" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D98" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="H98" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E98" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>255</v>
       </c>
       <c r="B99" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C99" s="1"/>
-      <c r="D99" s="1"/>
-      <c r="E99" s="1"/>
-      <c r="F99" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G99" s="3" t="s">
+      <c r="C99" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="H99" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E99" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>257</v>
       </c>
       <c r="B100" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G100" s="3" t="s">
+      <c r="C100" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D100" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H100" s="3" t="s">
+      <c r="E100" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>259</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="1"/>
-      <c r="D101" s="1"/>
-      <c r="E101" s="1"/>
-      <c r="F101" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G101" s="3" t="s">
+      <c r="C101" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="H101" s="3" t="s">
+      <c r="E101" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>261</v>
       </c>
       <c r="B102" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G102" s="3" t="s">
+      <c r="C102" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D102" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="H102" s="3" t="s">
+      <c r="E102" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>263</v>
       </c>
       <c r="B103" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C103" s="1"/>
-      <c r="D103" s="1"/>
-      <c r="E103" s="1"/>
-      <c r="F103" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G103" s="3" t="s">
+      <c r="C103" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D103" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H103" s="3" t="s">
+      <c r="E103" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>265</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C104" s="1"/>
-      <c r="D104" s="1"/>
-      <c r="E104" s="1"/>
-      <c r="F104" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G104" s="3" t="s">
+      <c r="C104" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D104" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H104" s="3" t="s">
+      <c r="E104" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>267</v>
       </c>
       <c r="B105" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C105" s="1"/>
-      <c r="D105" s="1"/>
-      <c r="E105" s="1"/>
-      <c r="F105" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G105" s="3" t="s">
+      <c r="C105" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D105" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="H105" s="3" t="s">
+      <c r="E105" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>269</v>
       </c>
       <c r="B106" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C106" s="1"/>
-      <c r="D106" s="1"/>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G106" s="3" t="s">
+      <c r="C106" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D106" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="H106" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E106" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>272</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C107" s="1"/>
-      <c r="D107" s="1"/>
-      <c r="E107" s="1"/>
-      <c r="F107" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G107" s="3" t="s">
+      <c r="C107" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D107" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="H107" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E107" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>275</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C108" s="1"/>
-      <c r="D108" s="1"/>
-      <c r="E108" s="1"/>
-      <c r="F108" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G108" s="3" t="s">
+      <c r="C108" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D108" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="H108" s="3" t="s">
+      <c r="E108" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>279</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C109" s="1"/>
-      <c r="D109" s="1"/>
-      <c r="E109" s="1"/>
-      <c r="F109" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G109" s="3" t="s">
+      <c r="C109" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D109" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="H109" s="3" t="s">
+      <c r="E109" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>282</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C110" s="1"/>
-      <c r="D110" s="1"/>
-      <c r="E110" s="1"/>
-      <c r="F110" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G110" s="3" t="s">
+      <c r="C110" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="H110" s="3" t="s">
+      <c r="E110" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>285</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C111" s="1"/>
-      <c r="D111" s="1"/>
-      <c r="E111" s="1"/>
-      <c r="F111" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G111" s="3" t="s">
+      <c r="C111" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D111" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="H111" s="3" t="s">
+      <c r="E111" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>288</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C112" s="1"/>
-      <c r="D112" s="1"/>
-      <c r="E112" s="1"/>
-      <c r="F112" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G112" s="3" t="s">
+      <c r="C112" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D112" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="H112" s="3" t="s">
+      <c r="E112" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>291</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C113" s="1"/>
-      <c r="D113" s="1"/>
-      <c r="E113" s="1"/>
-      <c r="F113" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G113" s="3" t="s">
+      <c r="C113" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="H113" s="3" t="s">
+      <c r="E113" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>294</v>
       </c>
       <c r="B114" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G114" s="3" t="s">
+      <c r="C114" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D114" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="H114" s="3" t="s">
+      <c r="E114" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>297</v>
       </c>
       <c r="B115" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G115" s="3" t="s">
+      <c r="C115" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D115" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="H115" s="3" t="s">
+      <c r="E115" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>300</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G116" s="3" t="s">
+      <c r="C116" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D116" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="H116" s="3" t="s">
+      <c r="E116" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>303</v>
       </c>
       <c r="B117" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G117" s="3" t="s">
+      <c r="C117" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D117" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="H117" s="3" t="s">
+      <c r="E117" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>306</v>
       </c>
       <c r="B118" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C118" s="1"/>
-      <c r="D118" s="1"/>
-      <c r="E118" s="1"/>
-      <c r="F118" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G118" s="3" t="s">
+      <c r="C118" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D118" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="H118" s="3" t="s">
+      <c r="E118" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>309</v>
       </c>
       <c r="B119" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C119" s="1"/>
-      <c r="D119" s="1"/>
-      <c r="E119" s="1"/>
-      <c r="F119" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G119" s="3" t="s">
+      <c r="C119" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D119" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="H119" s="3" t="s">
+      <c r="E119" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>312</v>
       </c>
       <c r="B120" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C120" s="1"/>
-      <c r="D120" s="1"/>
-      <c r="E120" s="1"/>
-      <c r="F120" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G120" s="3" t="s">
+      <c r="C120" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D120" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="H120" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E120" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>315</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C121" s="1"/>
-      <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G121" s="3" t="s">
+      <c r="C121" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D121" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="H121" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E121" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>318</v>
       </c>
       <c r="B122" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C122" s="1"/>
-      <c r="D122" s="1"/>
-      <c r="E122" s="1"/>
-      <c r="F122" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G122" s="3" t="s">
+      <c r="C122" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D122" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H122" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E122" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>321</v>
       </c>
       <c r="B123" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C123" s="1"/>
-      <c r="D123" s="1"/>
-      <c r="E123" s="1"/>
-      <c r="F123" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G123" s="3" t="s">
+      <c r="C123" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D123" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="H123" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E123" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>324</v>
       </c>
       <c r="B124" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C124" s="1"/>
-      <c r="D124" s="1"/>
-      <c r="E124" s="1"/>
-      <c r="F124" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G124" s="3" t="s">
+      <c r="C124" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D124" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="H124" s="3" t="s">
+      <c r="E124" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>328</v>
       </c>
       <c r="B125" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C125" s="1"/>
-      <c r="D125" s="1"/>
-      <c r="E125" s="1"/>
-      <c r="F125" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G125" s="3" t="s">
+      <c r="C125" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D125" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="H125" s="3" t="s">
+      <c r="E125" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
       <c r="B126" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C126" s="1"/>
-      <c r="D126" s="1"/>
-      <c r="E126" s="1"/>
-      <c r="F126" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G126" s="3" t="s">
+      <c r="C126" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D126" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="H126" s="3" t="s">
+      <c r="E126" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>335</v>
       </c>
       <c r="B127" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C127" s="1"/>
-      <c r="D127" s="1"/>
-      <c r="E127" s="1"/>
-      <c r="F127" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G127" s="3" t="s">
+      <c r="C127" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D127" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="H127" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E127" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>338</v>
       </c>
       <c r="B128" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C128" s="1"/>
-      <c r="D128" s="1"/>
-      <c r="E128" s="1"/>
-      <c r="F128" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G128" s="3" t="s">
+      <c r="C128" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D128" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="H128" s="3" t="s">
+      <c r="E128" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>341</v>
       </c>
       <c r="B129" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="D129" s="1"/>
-      <c r="E129" s="1"/>
-      <c r="F129" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G129" s="3" t="s">
+      <c r="C129" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D129" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="H129" s="3" t="s">
+      <c r="E129" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>344</v>
       </c>
       <c r="B130" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C130" s="1"/>
-      <c r="D130" s="1"/>
-      <c r="E130" s="1"/>
-      <c r="F130" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G130" s="3" t="s">
+      <c r="C130" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D130" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="H130" s="3" t="s">
+      <c r="E130" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>346</v>
       </c>
       <c r="B131" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C131" s="1"/>
-      <c r="D131" s="1"/>
-      <c r="E131" s="1"/>
-      <c r="F131" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G131" s="3" t="s">
+      <c r="C131" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D131" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="H131" s="3" t="s">
+      <c r="E131" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>348</v>
       </c>
       <c r="B132" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C132" s="1"/>
-      <c r="D132" s="1"/>
-      <c r="E132" s="1"/>
-      <c r="F132" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G132" s="3" t="s">
+      <c r="C132" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D132" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="H132" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E132" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>350</v>
       </c>
       <c r="B133" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C133" s="1"/>
-      <c r="D133" s="1"/>
-      <c r="E133" s="1"/>
-      <c r="F133" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G133" s="3" t="s">
+      <c r="C133" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D133" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="H133" s="3" t="s">
+      <c r="E133" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>353</v>
       </c>
       <c r="B134" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C134" s="1"/>
-      <c r="D134" s="1"/>
-      <c r="E134" s="1"/>
-      <c r="F134" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G134" s="3" t="s">
+      <c r="C134" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D134" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="H134" s="3" t="s">
+      <c r="E134" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>355</v>
       </c>
       <c r="B135" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
-      <c r="F135" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G135" s="3" t="s">
+      <c r="C135" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="H135" s="3" t="s">
+      <c r="E135" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B136" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C136" s="1"/>
-      <c r="D136" s="1"/>
-      <c r="E136" s="1"/>
-      <c r="F136" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G136" s="3" t="s">
+      <c r="C136" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D136" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="H136" s="3" t="s">
+      <c r="E136" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>359</v>
       </c>
       <c r="B137" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C137" s="1"/>
-      <c r="D137" s="1"/>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G137" s="3" t="s">
+      <c r="C137" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="H137" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E137" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>361</v>
       </c>
       <c r="B138" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C138" s="1"/>
-      <c r="D138" s="1"/>
-      <c r="E138" s="1"/>
-      <c r="F138" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G138" s="3" t="s">
+      <c r="C138" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D138" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="H138" s="3" t="s">
+      <c r="E138" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>363</v>
       </c>
       <c r="B139" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C139" s="1"/>
-      <c r="D139" s="1"/>
-      <c r="E139" s="1"/>
-      <c r="F139" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G139" s="3" t="s">
+      <c r="C139" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D139" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="H139" s="3" t="s">
+      <c r="E139" s="3" t="s">
         <v>331</v>
       </c>
     </row>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.yuldashev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867AD7C5-032E-403D-B579-B24DFB36465A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2066D0-F83B-4928-A8F1-2B10C0D39400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="270" yWindow="0" windowWidth="18360" windowHeight="15195" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
     <sheet name="A80-MSS-PC-100" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'A80-MSS-PC-100'!$A$1:$E$139</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'A80-MSS-PC-100'!$A$1:$F$139</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="372">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -1150,6 +1150,9 @@
   </si>
   <si>
     <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
   </si>
 </sst>
 </file>
@@ -1567,17 +1570,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:F139"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
     <col min="2" max="2" width="63" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17" style="6" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="16.140625" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.42578125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>366</v>
       </c>
@@ -1593,8 +1596,11 @@
       <c r="E1" s="8" t="s">
         <v>370</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="8" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1607,11 +1613,14 @@
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E2" s="3">
+        <v>1</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1624,11 +1633,14 @@
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -1641,11 +1653,14 @@
       <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E4" s="3">
+        <v>3</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -1658,11 +1673,14 @@
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="3">
+        <v>4</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1675,11 +1693,14 @@
       <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="3">
+        <v>5</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -1692,11 +1713,14 @@
       <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E7" s="3">
+        <v>6</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -1709,11 +1733,14 @@
       <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E8" s="3">
+        <v>7</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1726,11 +1753,14 @@
       <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E9" s="3">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1743,11 +1773,14 @@
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E10" s="3">
+        <v>9</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>26</v>
       </c>
@@ -1760,11 +1793,14 @@
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E11" s="3">
+        <v>10</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>28</v>
       </c>
@@ -1777,11 +1813,14 @@
       <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E12" s="3">
+        <v>11</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>30</v>
       </c>
@@ -1794,11 +1833,14 @@
       <c r="D13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="3">
+        <v>12</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -1811,11 +1853,14 @@
       <c r="D14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E14" s="3">
+        <v>13</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>34</v>
       </c>
@@ -1828,11 +1873,14 @@
       <c r="D15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E15" s="3">
+        <v>14</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>36</v>
       </c>
@@ -1845,11 +1893,14 @@
       <c r="D16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E16" s="3">
+        <v>15</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>38</v>
       </c>
@@ -1862,11 +1913,14 @@
       <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E17" s="3">
+        <v>16</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>40</v>
       </c>
@@ -1879,11 +1933,14 @@
       <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E18" s="3">
+        <v>17</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>42</v>
       </c>
@@ -1896,11 +1953,14 @@
       <c r="D19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E19" s="3">
+        <v>18</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>44</v>
       </c>
@@ -1913,11 +1973,14 @@
       <c r="D20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E20" s="3">
+        <v>19</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>46</v>
       </c>
@@ -1930,11 +1993,14 @@
       <c r="D21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E21" s="3">
+        <v>20</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>49</v>
       </c>
@@ -1947,11 +2013,14 @@
       <c r="D22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E22" s="3">
+        <v>21</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>52</v>
       </c>
@@ -1964,11 +2033,14 @@
       <c r="D23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E23" s="3">
+        <v>22</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>55</v>
       </c>
@@ -1981,11 +2053,14 @@
       <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E24" s="3">
+        <v>23</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>58</v>
       </c>
@@ -1998,11 +2073,14 @@
       <c r="D25" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" s="3">
+        <v>24</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>61</v>
       </c>
@@ -2015,11 +2093,14 @@
       <c r="D26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E26" s="3">
+        <v>25</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>64</v>
       </c>
@@ -2032,11 +2113,14 @@
       <c r="D27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E27" s="3">
+        <v>26</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>67</v>
       </c>
@@ -2049,11 +2133,14 @@
       <c r="D28" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="3" t="s">
+      <c r="E28" s="3">
+        <v>27</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>71</v>
       </c>
@@ -2066,11 +2153,14 @@
       <c r="D29" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="3" t="s">
+      <c r="E29" s="3">
+        <v>28</v>
+      </c>
+      <c r="F29" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>74</v>
       </c>
@@ -2083,11 +2173,14 @@
       <c r="D30" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E30" s="3" t="s">
+      <c r="E30" s="3">
+        <v>29</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>76</v>
       </c>
@@ -2100,11 +2193,14 @@
       <c r="D31" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="3" t="s">
+      <c r="E31" s="3">
+        <v>30</v>
+      </c>
+      <c r="F31" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>78</v>
       </c>
@@ -2117,11 +2213,14 @@
       <c r="D32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="3" t="s">
+      <c r="E32" s="3">
+        <v>31</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>80</v>
       </c>
@@ -2134,11 +2233,14 @@
       <c r="D33" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="3" t="s">
+      <c r="E33" s="3">
+        <v>32</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>83</v>
       </c>
@@ -2151,11 +2253,14 @@
       <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="3">
+        <v>33</v>
+      </c>
+      <c r="F34" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>87</v>
       </c>
@@ -2168,11 +2273,14 @@
       <c r="D35" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E35" s="3" t="s">
+      <c r="E35" s="3">
+        <v>34</v>
+      </c>
+      <c r="F35" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>90</v>
       </c>
@@ -2185,11 +2293,14 @@
       <c r="D36" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E36" s="3" t="s">
+      <c r="E36" s="3">
+        <v>35</v>
+      </c>
+      <c r="F36" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>93</v>
       </c>
@@ -2202,11 +2313,14 @@
       <c r="D37" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E37" s="3" t="s">
+      <c r="E37" s="3">
+        <v>36</v>
+      </c>
+      <c r="F37" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>96</v>
       </c>
@@ -2219,11 +2333,14 @@
       <c r="D38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E38" s="3" t="s">
+      <c r="E38" s="3">
+        <v>37</v>
+      </c>
+      <c r="F38" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>99</v>
       </c>
@@ -2236,11 +2353,14 @@
       <c r="D39" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="3" t="s">
+      <c r="E39" s="3">
+        <v>38</v>
+      </c>
+      <c r="F39" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>102</v>
       </c>
@@ -2253,11 +2373,14 @@
       <c r="D40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E40" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E40" s="3">
+        <v>39</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>105</v>
       </c>
@@ -2270,11 +2393,14 @@
       <c r="D41" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E41" s="3" t="s">
+      <c r="E41" s="3">
+        <v>40</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>108</v>
       </c>
@@ -2287,11 +2413,14 @@
       <c r="D42" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E42" s="3">
+        <v>41</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>111</v>
       </c>
@@ -2304,11 +2433,14 @@
       <c r="D43" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E43" s="3" t="s">
+      <c r="E43" s="3">
+        <v>42</v>
+      </c>
+      <c r="F43" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>114</v>
       </c>
@@ -2321,11 +2453,14 @@
       <c r="D44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="E44" s="3">
+        <v>43</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>118</v>
       </c>
@@ -2338,11 +2473,14 @@
       <c r="D45" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="3" t="s">
+      <c r="E45" s="3">
+        <v>44</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>120</v>
       </c>
@@ -2355,11 +2493,14 @@
       <c r="D46" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E46" s="3" t="s">
+      <c r="E46" s="3">
+        <v>45</v>
+      </c>
+      <c r="F46" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>123</v>
       </c>
@@ -2372,11 +2513,14 @@
       <c r="D47" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E47" s="3" t="s">
+      <c r="E47" s="3">
+        <v>46</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>125</v>
       </c>
@@ -2389,11 +2533,14 @@
       <c r="D48" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="3" t="s">
+      <c r="E48" s="3">
+        <v>47</v>
+      </c>
+      <c r="F48" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>129</v>
       </c>
@@ -2406,11 +2553,14 @@
       <c r="D49" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="E49" s="3">
+        <v>48</v>
+      </c>
+      <c r="F49" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>132</v>
       </c>
@@ -2423,11 +2573,14 @@
       <c r="D50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="E50" s="3">
+        <v>49</v>
+      </c>
+      <c r="F50" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>135</v>
       </c>
@@ -2440,11 +2593,14 @@
       <c r="D51" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="E51" s="3">
+        <v>50</v>
+      </c>
+      <c r="F51" s="3" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>138</v>
       </c>
@@ -2457,11 +2613,14 @@
       <c r="D52" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="E52" s="3">
+        <v>51</v>
+      </c>
+      <c r="F52" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>142</v>
       </c>
@@ -2474,11 +2633,14 @@
       <c r="D53" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="E53" s="3">
+        <v>52</v>
+      </c>
+      <c r="F53" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>144</v>
       </c>
@@ -2491,11 +2653,14 @@
       <c r="D54" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="E54" s="3">
+        <v>53</v>
+      </c>
+      <c r="F54" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>147</v>
       </c>
@@ -2508,11 +2673,14 @@
       <c r="D55" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="E55" s="3">
+        <v>54</v>
+      </c>
+      <c r="F55" s="3" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>149</v>
       </c>
@@ -2525,11 +2693,14 @@
       <c r="D56" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="E56" s="3">
+        <v>55</v>
+      </c>
+      <c r="F56" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>152</v>
       </c>
@@ -2542,11 +2713,14 @@
       <c r="D57" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E57" s="3">
+        <v>56</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>155</v>
       </c>
@@ -2559,11 +2733,14 @@
       <c r="D58" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E58" s="3" t="s">
+      <c r="E58" s="3">
+        <v>57</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>158</v>
       </c>
@@ -2576,11 +2753,14 @@
       <c r="D59" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="E59" s="3">
+        <v>58</v>
+      </c>
+      <c r="F59" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>161</v>
       </c>
@@ -2593,11 +2773,14 @@
       <c r="D60" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E60" s="3" t="s">
+      <c r="E60" s="3">
+        <v>59</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>164</v>
       </c>
@@ -2610,11 +2793,14 @@
       <c r="D61" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="E61" s="3">
+        <v>60</v>
+      </c>
+      <c r="F61" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>167</v>
       </c>
@@ -2627,11 +2813,14 @@
       <c r="D62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="3" t="s">
+      <c r="E62" s="3">
+        <v>61</v>
+      </c>
+      <c r="F62" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>170</v>
       </c>
@@ -2644,11 +2833,14 @@
       <c r="D63" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E63" s="3" t="s">
+      <c r="E63" s="3">
+        <v>62</v>
+      </c>
+      <c r="F63" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>173</v>
       </c>
@@ -2661,11 +2853,14 @@
       <c r="D64" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E64" s="3" t="s">
+      <c r="E64" s="3">
+        <v>63</v>
+      </c>
+      <c r="F64" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>176</v>
       </c>
@@ -2678,11 +2873,14 @@
       <c r="D65" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E65" s="3" t="s">
+      <c r="E65" s="3">
+        <v>64</v>
+      </c>
+      <c r="F65" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>179</v>
       </c>
@@ -2695,11 +2893,14 @@
       <c r="D66" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E66" s="3" t="s">
+      <c r="E66" s="3">
+        <v>65</v>
+      </c>
+      <c r="F66" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>182</v>
       </c>
@@ -2712,11 +2913,14 @@
       <c r="D67" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="E67" s="3">
+        <v>66</v>
+      </c>
+      <c r="F67" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>185</v>
       </c>
@@ -2729,11 +2933,14 @@
       <c r="D68" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E68" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E68" s="3">
+        <v>67</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>188</v>
       </c>
@@ -2746,11 +2953,14 @@
       <c r="D69" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E69" s="3">
+        <v>68</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>191</v>
       </c>
@@ -2763,11 +2973,14 @@
       <c r="D70" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="E70" s="3">
+        <v>69</v>
+      </c>
+      <c r="F70" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>194</v>
       </c>
@@ -2780,11 +2993,14 @@
       <c r="D71" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E71" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E71" s="3">
+        <v>70</v>
+      </c>
+      <c r="F71" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>197</v>
       </c>
@@ -2797,11 +3013,14 @@
       <c r="D72" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E72" s="3">
+        <v>71</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>200</v>
       </c>
@@ -2814,11 +3033,14 @@
       <c r="D73" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E73" s="3" t="s">
+      <c r="E73" s="3">
+        <v>72</v>
+      </c>
+      <c r="F73" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>203</v>
       </c>
@@ -2831,11 +3053,14 @@
       <c r="D74" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E74" s="3">
+        <v>73</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>206</v>
       </c>
@@ -2848,12 +3073,15 @@
       <c r="D75" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E75" s="3" t="str">
-        <f>$E$65</f>
+      <c r="E75" s="3">
+        <v>74</v>
+      </c>
+      <c r="F75" s="3" t="str">
+        <f>$F$65</f>
         <v>LF-02A</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>209</v>
       </c>
@@ -2866,11 +3094,14 @@
       <c r="D76" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E76" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E76" s="3">
+        <v>75</v>
+      </c>
+      <c r="F76" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>212</v>
       </c>
@@ -2883,11 +3114,14 @@
       <c r="D77" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E77" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E77" s="3">
+        <v>76</v>
+      </c>
+      <c r="F77" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>215</v>
       </c>
@@ -2900,11 +3134,14 @@
       <c r="D78" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E78" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E78" s="3">
+        <v>77</v>
+      </c>
+      <c r="F78" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>217</v>
       </c>
@@ -2917,11 +3154,14 @@
       <c r="D79" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E79" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E79" s="3">
+        <v>78</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>219</v>
       </c>
@@ -2934,11 +3174,14 @@
       <c r="D80" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E80" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E80" s="3">
+        <v>79</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>219</v>
       </c>
@@ -2951,11 +3194,14 @@
       <c r="D81" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E81" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E81" s="3">
+        <v>80</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>222</v>
       </c>
@@ -2968,11 +3214,14 @@
       <c r="D82" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E82" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E82" s="3">
+        <v>81</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>222</v>
       </c>
@@ -2985,11 +3234,14 @@
       <c r="D83" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E83" s="3">
+        <v>82</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>225</v>
       </c>
@@ -3002,11 +3254,14 @@
       <c r="D84" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E84" s="3">
+        <v>83</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>225</v>
       </c>
@@ -3019,11 +3274,14 @@
       <c r="D85" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E85" s="3" t="s">
+      <c r="E85" s="3">
+        <v>84</v>
+      </c>
+      <c r="F85" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>230</v>
       </c>
@@ -3036,11 +3294,14 @@
       <c r="D86" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E86" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E86" s="3">
+        <v>85</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>232</v>
       </c>
@@ -3053,11 +3314,14 @@
       <c r="D87" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E87" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E87" s="3">
+        <v>86</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>234</v>
       </c>
@@ -3070,11 +3334,14 @@
       <c r="D88" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E88" s="3" t="s">
+      <c r="E88" s="3">
+        <v>87</v>
+      </c>
+      <c r="F88" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>236</v>
       </c>
@@ -3087,11 +3354,14 @@
       <c r="D89" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E89" s="3" t="s">
+      <c r="E89" s="3">
+        <v>88</v>
+      </c>
+      <c r="F89" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>238</v>
       </c>
@@ -3104,11 +3374,14 @@
       <c r="D90" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E90" s="3" t="s">
+      <c r="E90" s="3">
+        <v>89</v>
+      </c>
+      <c r="F90" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>240</v>
       </c>
@@ -3121,11 +3394,14 @@
       <c r="D91" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E91" s="3" t="s">
+      <c r="E91" s="3">
+        <v>90</v>
+      </c>
+      <c r="F91" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>242</v>
       </c>
@@ -3138,11 +3414,14 @@
       <c r="D92" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E92" s="3" t="s">
+      <c r="E92" s="3">
+        <v>91</v>
+      </c>
+      <c r="F92" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>245</v>
       </c>
@@ -3155,11 +3434,14 @@
       <c r="D93" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E93" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E93" s="3">
+        <v>92</v>
+      </c>
+      <c r="F93" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>247</v>
       </c>
@@ -3172,11 +3454,14 @@
       <c r="D94" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E94" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E94" s="3">
+        <v>93</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>249</v>
       </c>
@@ -3189,11 +3474,14 @@
       <c r="D95" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E95" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E95" s="3">
+        <v>94</v>
+      </c>
+      <c r="F95" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>251</v>
       </c>
@@ -3206,11 +3494,14 @@
       <c r="D96" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E96" s="3">
+        <v>95</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>251</v>
       </c>
@@ -3223,11 +3514,14 @@
       <c r="D97" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E97" s="3">
+        <v>96</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>253</v>
       </c>
@@ -3240,11 +3534,14 @@
       <c r="D98" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E98" s="3">
+        <v>97</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>255</v>
       </c>
@@ -3257,11 +3554,14 @@
       <c r="D99" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E99" s="3">
+        <v>98</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>257</v>
       </c>
@@ -3274,11 +3574,14 @@
       <c r="D100" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E100" s="3" t="s">
+      <c r="E100" s="3">
+        <v>99</v>
+      </c>
+      <c r="F100" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>259</v>
       </c>
@@ -3291,11 +3594,14 @@
       <c r="D101" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="E101" s="3" t="s">
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>261</v>
       </c>
@@ -3308,11 +3614,14 @@
       <c r="D102" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E102" s="3" t="s">
+      <c r="E102" s="3">
+        <v>101</v>
+      </c>
+      <c r="F102" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>263</v>
       </c>
@@ -3325,11 +3634,14 @@
       <c r="D103" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E103" s="3" t="s">
+      <c r="E103" s="3">
+        <v>102</v>
+      </c>
+      <c r="F103" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>265</v>
       </c>
@@ -3342,11 +3654,14 @@
       <c r="D104" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E104" s="3" t="s">
+      <c r="E104" s="3">
+        <v>103</v>
+      </c>
+      <c r="F104" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>267</v>
       </c>
@@ -3359,11 +3674,14 @@
       <c r="D105" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E105" s="3" t="s">
+      <c r="E105" s="3">
+        <v>104</v>
+      </c>
+      <c r="F105" s="3" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>269</v>
       </c>
@@ -3376,11 +3694,14 @@
       <c r="D106" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E106" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E106" s="3">
+        <v>105</v>
+      </c>
+      <c r="F106" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>272</v>
       </c>
@@ -3393,11 +3714,14 @@
       <c r="D107" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E107" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E107" s="3">
+        <v>106</v>
+      </c>
+      <c r="F107" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>275</v>
       </c>
@@ -3410,11 +3734,14 @@
       <c r="D108" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E108" s="3" t="s">
+      <c r="E108" s="3">
+        <v>107</v>
+      </c>
+      <c r="F108" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>279</v>
       </c>
@@ -3427,11 +3754,14 @@
       <c r="D109" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E109" s="3" t="s">
+      <c r="E109" s="3">
+        <v>108</v>
+      </c>
+      <c r="F109" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>282</v>
       </c>
@@ -3444,11 +3774,14 @@
       <c r="D110" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E110" s="3" t="s">
+      <c r="E110" s="3">
+        <v>109</v>
+      </c>
+      <c r="F110" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>285</v>
       </c>
@@ -3461,11 +3794,14 @@
       <c r="D111" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E111" s="3" t="s">
+      <c r="E111" s="3">
+        <v>110</v>
+      </c>
+      <c r="F111" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>288</v>
       </c>
@@ -3478,11 +3814,14 @@
       <c r="D112" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E112" s="3" t="s">
+      <c r="E112" s="3">
+        <v>111</v>
+      </c>
+      <c r="F112" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>291</v>
       </c>
@@ -3495,11 +3834,14 @@
       <c r="D113" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E113" s="3" t="s">
+      <c r="E113" s="3">
+        <v>112</v>
+      </c>
+      <c r="F113" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>294</v>
       </c>
@@ -3512,11 +3854,14 @@
       <c r="D114" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E114" s="3" t="s">
+      <c r="E114" s="3">
+        <v>113</v>
+      </c>
+      <c r="F114" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>297</v>
       </c>
@@ -3529,11 +3874,14 @@
       <c r="D115" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E115" s="3" t="s">
+      <c r="E115" s="3">
+        <v>114</v>
+      </c>
+      <c r="F115" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>300</v>
       </c>
@@ -3546,11 +3894,14 @@
       <c r="D116" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E116" s="3" t="s">
+      <c r="E116" s="3">
+        <v>115</v>
+      </c>
+      <c r="F116" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>303</v>
       </c>
@@ -3563,11 +3914,14 @@
       <c r="D117" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E117" s="3" t="s">
+      <c r="E117" s="3">
+        <v>116</v>
+      </c>
+      <c r="F117" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>306</v>
       </c>
@@ -3580,11 +3934,14 @@
       <c r="D118" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="E118" s="3" t="s">
+      <c r="E118" s="3">
+        <v>117</v>
+      </c>
+      <c r="F118" s="3" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>309</v>
       </c>
@@ -3597,11 +3954,14 @@
       <c r="D119" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E119" s="3" t="s">
+      <c r="E119" s="3">
+        <v>118</v>
+      </c>
+      <c r="F119" s="3" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>312</v>
       </c>
@@ -3614,11 +3974,14 @@
       <c r="D120" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="E120" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E120" s="3">
+        <v>119</v>
+      </c>
+      <c r="F120" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>315</v>
       </c>
@@ -3631,11 +3994,14 @@
       <c r="D121" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E121" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E121" s="3">
+        <v>120</v>
+      </c>
+      <c r="F121" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>318</v>
       </c>
@@ -3648,11 +4014,14 @@
       <c r="D122" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E122" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E122" s="3">
+        <v>121</v>
+      </c>
+      <c r="F122" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>321</v>
       </c>
@@ -3665,11 +4034,14 @@
       <c r="D123" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="E123" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E123" s="3">
+        <v>122</v>
+      </c>
+      <c r="F123" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>324</v>
       </c>
@@ -3682,11 +4054,14 @@
       <c r="D124" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E124" s="3" t="s">
+      <c r="E124" s="3">
+        <v>123</v>
+      </c>
+      <c r="F124" s="3" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>328</v>
       </c>
@@ -3699,11 +4074,14 @@
       <c r="D125" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E125" s="3" t="s">
+      <c r="E125" s="3">
+        <v>124</v>
+      </c>
+      <c r="F125" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>332</v>
       </c>
@@ -3716,11 +4094,14 @@
       <c r="D126" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E126" s="3" t="s">
+      <c r="E126" s="3">
+        <v>125</v>
+      </c>
+      <c r="F126" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>335</v>
       </c>
@@ -3733,11 +4114,14 @@
       <c r="D127" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E127" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E127" s="3">
+        <v>126</v>
+      </c>
+      <c r="F127" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>338</v>
       </c>
@@ -3750,11 +4134,14 @@
       <c r="D128" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E128" s="3" t="s">
+      <c r="E128" s="3">
+        <v>127</v>
+      </c>
+      <c r="F128" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>341</v>
       </c>
@@ -3767,11 +4154,14 @@
       <c r="D129" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E129" s="3" t="s">
+      <c r="E129" s="3">
+        <v>128</v>
+      </c>
+      <c r="F129" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>344</v>
       </c>
@@ -3784,11 +4174,14 @@
       <c r="D130" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E130" s="3" t="s">
+      <c r="E130" s="3">
+        <v>129</v>
+      </c>
+      <c r="F130" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>346</v>
       </c>
@@ -3801,11 +4194,14 @@
       <c r="D131" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E131" s="3" t="s">
+      <c r="E131" s="3">
+        <v>130</v>
+      </c>
+      <c r="F131" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>348</v>
       </c>
@@ -3818,11 +4214,14 @@
       <c r="D132" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E132" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E132" s="3">
+        <v>131</v>
+      </c>
+      <c r="F132" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>350</v>
       </c>
@@ -3835,11 +4234,14 @@
       <c r="D133" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E133" s="3" t="s">
+      <c r="E133" s="3">
+        <v>132</v>
+      </c>
+      <c r="F133" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>353</v>
       </c>
@@ -3852,11 +4254,14 @@
       <c r="D134" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E134" s="3" t="s">
+      <c r="E134" s="3">
+        <v>133</v>
+      </c>
+      <c r="F134" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>355</v>
       </c>
@@ -3869,11 +4274,14 @@
       <c r="D135" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="E135" s="3" t="s">
+      <c r="E135" s="3">
+        <v>134</v>
+      </c>
+      <c r="F135" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>357</v>
       </c>
@@ -3886,11 +4294,14 @@
       <c r="D136" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E136" s="3" t="s">
+      <c r="E136" s="3">
+        <v>135</v>
+      </c>
+      <c r="F136" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>359</v>
       </c>
@@ -3903,11 +4314,14 @@
       <c r="D137" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="E137" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E137" s="3">
+        <v>136</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>361</v>
       </c>
@@ -3920,11 +4334,14 @@
       <c r="D138" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E138" s="3" t="s">
+      <c r="E138" s="3">
+        <v>137</v>
+      </c>
+      <c r="F138" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>363</v>
       </c>
@@ -3937,7 +4354,10 @@
       <c r="D139" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E139" s="3" t="s">
+      <c r="E139" s="3">
+        <v>138</v>
+      </c>
+      <c r="F139" s="3" t="s">
         <v>331</v>
       </c>
     </row>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.yuldashev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F2066D0-F83B-4928-A8F1-2B10C0D39400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5F146E-D80F-4BD9-BABE-1D17139F5B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
   <sheets>
-    <sheet name="A80-MSS-PC-100" sheetId="1" r:id="rId1"/>
+    <sheet name="mcc" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'A80-MSS-PC-100'!$A$1:$F$139</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">mcc!$A$1:$F$167</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="836" uniqueCount="426">
   <si>
     <t>A80-ASU-LSP-006</t>
   </si>
@@ -1153,6 +1153,168 @@
   </si>
   <si>
     <t>F</t>
+  </si>
+  <si>
+    <t>A80-RBA-UPSA-001-B</t>
+  </si>
+  <si>
+    <t>CABLE TERMINATION COMPARTMENT</t>
+  </si>
+  <si>
+    <t>A80-ADM-TR-011</t>
+  </si>
+  <si>
+    <t>DRY TR. FOR EMERGENCY POWER DB (A80-ADM-EP-001)</t>
+  </si>
+  <si>
+    <t>A80-MSS-TR-011</t>
+  </si>
+  <si>
+    <t>DRY TR. FOR EMERGENCY POWER DB (A80-MSS-EP-001)</t>
+  </si>
+  <si>
+    <t>A80-MSS-UPSD-201-2</t>
+  </si>
+  <si>
+    <t>INSTRUMENT UPS (BYPASS)</t>
+  </si>
+  <si>
+    <t>A80-RBA-UPSA-101-B</t>
+  </si>
+  <si>
+    <t>COMMUNICATION UPS (BYPASS)</t>
+  </si>
+  <si>
+    <t>BTL10-BPD-A</t>
+  </si>
+  <si>
+    <t>GAS TURBINE BATTERY CHARGER (X-8801A-08)</t>
+  </si>
+  <si>
+    <t>BTL10-BPD-B</t>
+  </si>
+  <si>
+    <t>GAS TURBINE BATTERY CHARGER (X-8801B-08)</t>
+  </si>
+  <si>
+    <t>BTL10-BPD-C</t>
+  </si>
+  <si>
+    <t>GAS TURBINE BATTERY CHARGER (X-8801C-08)</t>
+  </si>
+  <si>
+    <t>K-8501A-H1</t>
+  </si>
+  <si>
+    <t>K-8501A-MP2</t>
+  </si>
+  <si>
+    <t>AIR COMPRESSOR TURBINE DRIVEN AUX. L/O PUMP</t>
+  </si>
+  <si>
+    <t>K-8501B-H1</t>
+  </si>
+  <si>
+    <t>K-8501B-MP2</t>
+  </si>
+  <si>
+    <t>MBJ10AE005-A</t>
+  </si>
+  <si>
+    <t>GAS TURBINE STARTER MOTOR (X-8801A-MK1) - BPD14</t>
+  </si>
+  <si>
+    <t>MBJ10AE005-B</t>
+  </si>
+  <si>
+    <t>GAS TURBINE STARTER MOTOR (X-8801B-MK1) - BPD14</t>
+  </si>
+  <si>
+    <t>MBJ10AE005-C</t>
+  </si>
+  <si>
+    <t>GAS TURBINE STARTER MOTOR (X-8801C-MK1)</t>
+  </si>
+  <si>
+    <t>MBV10AH005-A</t>
+  </si>
+  <si>
+    <t>GAS TURBINE L/O HEATER (X-8801A-ME7)</t>
+  </si>
+  <si>
+    <t>MBV10AH005-B</t>
+  </si>
+  <si>
+    <t>GAS TURBINE L/O HEATER (X-8801B-ME7)</t>
+  </si>
+  <si>
+    <t>MBV10AH005-C</t>
+  </si>
+  <si>
+    <t>GAS TURBINE L/O HEATER (X-8801C-ME7)</t>
+  </si>
+  <si>
+    <t>P-8303A-P02</t>
+  </si>
+  <si>
+    <t>P-8303S-P02</t>
+  </si>
+  <si>
+    <t>HHP BFW PUMP MOTOR AUX. L/O PUMP</t>
+  </si>
+  <si>
+    <t>P-8304A-P02</t>
+  </si>
+  <si>
+    <t>HP BFW PUMP TURBINE L/O PUMP</t>
+  </si>
+  <si>
+    <t>P-8304S-P02</t>
+  </si>
+  <si>
+    <t>HP BFW PUMP MOTOR LUBE OIL PUMP</t>
+  </si>
+  <si>
+    <t>T-8401A-ME6</t>
+  </si>
+  <si>
+    <t>STEAM GENERATOR PACKAGE TURBINE CONTROL PANEL FOR LUBE OIL SYSTEM A</t>
+  </si>
+  <si>
+    <t>T-8401B-ME6</t>
+  </si>
+  <si>
+    <t>STEAM GENERATOR PACKAGE TURBINE CONTROL PANEL FOR LUBE OIL SYSTEM B</t>
+  </si>
+  <si>
+    <t>X-8502-T1</t>
+  </si>
+  <si>
+    <t>NITROGEN GENERATION PFG EXPANSION TURBINE</t>
+  </si>
+  <si>
+    <t>A80-MSS-PC-200</t>
+  </si>
+  <si>
+    <t>A1F-5</t>
+  </si>
+  <si>
+    <t>A2F-7</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>LF-01B</t>
+  </si>
+  <si>
+    <t>LM-51A</t>
+  </si>
+  <si>
+    <t>LF-04B</t>
+  </si>
+  <si>
+    <t>LM-34B</t>
   </si>
 </sst>
 </file>
@@ -1195,12 +1357,18 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -1233,7 +1401,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1254,7 +1422,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1570,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8965338B-7266-40B4-AF74-1B53A17A4909}">
-  <dimension ref="A1:F139"/>
+  <dimension ref="A1:F167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" customWidth="1"/>
@@ -4361,6 +4537,566 @@
         <v>331</v>
       </c>
     </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F140" s="3" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E141" s="1">
+        <v>70</v>
+      </c>
+      <c r="F141" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E142" s="1">
+        <v>150</v>
+      </c>
+      <c r="F142" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E143" s="1">
+        <v>32</v>
+      </c>
+      <c r="F143" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" s="1">
+        <v>104</v>
+      </c>
+      <c r="F144" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="E145" s="1">
+        <v>16</v>
+      </c>
+      <c r="F145" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" s="1">
+        <v>138.80000000000001</v>
+      </c>
+      <c r="F146" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D147" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E147" s="1">
+        <v>138.80000000000001</v>
+      </c>
+      <c r="F147" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D148" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E148" s="1">
+        <v>138.80000000000001</v>
+      </c>
+      <c r="F148" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D149" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E149" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F149" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D150" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E150" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="F150" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D151" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E151" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="F151" s="3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D152" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E152" s="1">
+        <v>5.6</v>
+      </c>
+      <c r="F152" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D153" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E153" s="1">
+        <v>150</v>
+      </c>
+      <c r="F153" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D154" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E154" s="1">
+        <v>150</v>
+      </c>
+      <c r="F154" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D155" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="E155" s="1">
+        <v>150</v>
+      </c>
+      <c r="F155" s="3" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E156" s="1">
+        <v>30</v>
+      </c>
+      <c r="F156" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="5" t="s">
+        <v>401</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>402</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D157" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="E157" s="1">
+        <v>30</v>
+      </c>
+      <c r="F157" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D158" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E158" s="1">
+        <v>30</v>
+      </c>
+      <c r="F158" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="B159" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D159" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E159" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F159" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D160" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E160" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F160" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D161" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E161" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F161" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D162" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E162" s="1">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F162" s="3" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D163" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E163" s="1">
+        <v>150</v>
+      </c>
+      <c r="F163" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D164" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="E164" s="1">
+        <v>50</v>
+      </c>
+      <c r="F164" s="3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D165" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="E165" s="1">
+        <v>6</v>
+      </c>
+      <c r="F165" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D166" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="E166" s="1">
+        <v>6</v>
+      </c>
+      <c r="F166" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="D167" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E167" s="1">
+        <v>12</v>
+      </c>
+      <c r="F167" s="3" t="s">
+        <v>422</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>

--- a/base.xlsx
+++ b/base.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m.yuldashev\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5F146E-D80F-4BD9-BABE-1D17139F5B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6385D764-1F65-4BAB-93F3-6D3799AA857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A158832D-4008-4E9C-A0F4-A1D2BE094D02}"/>
   </bookViews>
@@ -1321,7 +1321,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1355,6 +1355,13 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1783,14 +1790,14 @@
       <c r="B2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="3">
-        <v>1</v>
+      <c r="E2" s="1">
+        <v>18</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>4</v>
@@ -1803,14 +1810,14 @@
       <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="3">
-        <v>2</v>
+      <c r="E3" s="1">
+        <v>10.75</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>4</v>
@@ -1823,14 +1830,14 @@
       <c r="B4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="3">
-        <v>3</v>
+      <c r="E4" s="1">
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>4</v>
@@ -1843,14 +1850,14 @@
       <c r="B5" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3">
-        <v>4</v>
+      <c r="E5" s="1">
+        <v>1.5</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>14</v>
@@ -1863,14 +1870,14 @@
       <c r="B6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="3">
-        <v>5</v>
+      <c r="E6" s="1">
+        <v>1.5</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>14</v>
@@ -1883,14 +1890,14 @@
       <c r="B7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="3">
-        <v>6</v>
+      <c r="E7" s="1">
+        <v>111.8</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>4</v>
@@ -1903,14 +1910,14 @@
       <c r="B8" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="3">
-        <v>7</v>
+      <c r="E8" s="1">
+        <v>111.8</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>4</v>
@@ -1923,14 +1930,14 @@
       <c r="B9" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="3">
-        <v>8</v>
+      <c r="E9" s="1">
+        <v>111.8</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>4</v>
@@ -1943,14 +1950,14 @@
       <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="3">
-        <v>9</v>
+      <c r="E10" s="1">
+        <v>8.5</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>4</v>
@@ -1963,14 +1970,14 @@
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="3">
-        <v>10</v>
+      <c r="E11" s="1">
+        <v>8.5</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>4</v>
@@ -1983,14 +1990,14 @@
       <c r="B12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="3">
-        <v>11</v>
+      <c r="E12" s="1">
+        <v>8.5</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>4</v>
@@ -2003,14 +2010,14 @@
       <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E13" s="3">
-        <v>12</v>
+      <c r="E13" s="1">
+        <v>8.5</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>4</v>
@@ -2023,14 +2030,14 @@
       <c r="B14" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="3">
-        <v>13</v>
+      <c r="E14" s="1">
+        <v>8.5</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>4</v>
@@ -2043,14 +2050,14 @@
       <c r="B15" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E15" s="3">
-        <v>14</v>
+      <c r="E15" s="1">
+        <v>8.5</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>4</v>
@@ -2063,14 +2070,14 @@
       <c r="B16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="3">
-        <v>15</v>
+      <c r="E16" s="1">
+        <v>8.5</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>4</v>
@@ -2083,14 +2090,14 @@
       <c r="B17" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="3">
-        <v>16</v>
+      <c r="E17" s="1">
+        <v>8.5</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>4</v>
@@ -2103,14 +2110,14 @@
       <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D18" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="E18" s="3">
-        <v>17</v>
+      <c r="E18" s="1">
+        <v>8.5</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>4</v>
@@ -2123,14 +2130,14 @@
       <c r="B19" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D19" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E19" s="3">
-        <v>18</v>
+      <c r="E19" s="1">
+        <v>3.75</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>4</v>
@@ -2143,14 +2150,14 @@
       <c r="B20" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="E20" s="3">
-        <v>19</v>
+      <c r="E20" s="1">
+        <v>3.75</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>4</v>
@@ -2163,14 +2170,14 @@
       <c r="B21" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E21" s="3">
-        <v>20</v>
+      <c r="E21" s="1">
+        <v>100</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>4</v>
@@ -2183,14 +2190,14 @@
       <c r="B22" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="E22" s="3">
-        <v>21</v>
+      <c r="E22" s="1">
+        <v>150</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>4</v>
@@ -2203,14 +2210,14 @@
       <c r="B23" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="E23" s="3">
-        <v>22</v>
+      <c r="E23" s="1">
+        <v>32</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>4</v>
@@ -2223,14 +2230,14 @@
       <c r="B24" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="3">
-        <v>23</v>
+      <c r="E24" s="1">
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>4</v>
@@ -2243,14 +2250,14 @@
       <c r="B25" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="E25" s="3">
-        <v>24</v>
+      <c r="E25" s="1">
+        <v>10</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>4</v>
@@ -2263,14 +2270,14 @@
       <c r="B26" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D26" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E26" s="3">
-        <v>25</v>
+      <c r="E26" s="1">
+        <v>10</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>4</v>
@@ -2283,14 +2290,14 @@
       <c r="B27" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E27" s="3">
-        <v>26</v>
+      <c r="E27" s="1">
+        <v>4</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>4</v>
@@ -2303,14 +2310,14 @@
       <c r="B28" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="3">
-        <v>27</v>
+      <c r="E28" s="1">
+        <v>1.5</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>70</v>
@@ -2323,14 +2330,14 @@
       <c r="B29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E29" s="3">
-        <v>28</v>
+      <c r="E29" s="1">
+        <v>5.6</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>14</v>
@@ -2343,14 +2350,14 @@
       <c r="B30" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E30" s="3">
-        <v>29</v>
+      <c r="E30" s="1">
+        <v>1.5</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>70</v>
@@ -2363,14 +2370,14 @@
       <c r="B31" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D31" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E31" s="3">
-        <v>30</v>
+      <c r="E31" s="1">
+        <v>5.6</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>14</v>
@@ -2383,14 +2390,14 @@
       <c r="B32" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="3">
-        <v>31</v>
+      <c r="E32" s="1">
+        <v>1.5</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>70</v>
@@ -2403,14 +2410,14 @@
       <c r="B33" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D33" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="E33" s="3">
-        <v>32</v>
+      <c r="E33" s="1">
+        <v>5.6</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>14</v>
@@ -2423,14 +2430,14 @@
       <c r="B34" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="3">
-        <v>33</v>
+      <c r="E34" s="1">
+        <v>3</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>86</v>
@@ -2443,14 +2450,14 @@
       <c r="B35" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E35" s="3">
-        <v>34</v>
+      <c r="E35" s="1">
+        <v>3</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>86</v>
@@ -2463,14 +2470,14 @@
       <c r="B36" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E36" s="3">
-        <v>35</v>
+      <c r="E36" s="1">
+        <v>3</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>86</v>
@@ -2483,14 +2490,14 @@
       <c r="B37" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E37" s="3">
-        <v>36</v>
+      <c r="E37" s="1">
+        <v>3</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>86</v>
@@ -2503,14 +2510,14 @@
       <c r="B38" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E38" s="3">
-        <v>37</v>
+      <c r="E38" s="1">
+        <v>3</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>86</v>
@@ -2523,14 +2530,14 @@
       <c r="B39" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="E39" s="3">
-        <v>38</v>
+      <c r="E39" s="1">
+        <v>3</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>86</v>
@@ -2543,14 +2550,14 @@
       <c r="B40" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D40" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E40" s="3">
-        <v>39</v>
+      <c r="E40" s="1">
+        <v>12.85</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>4</v>
@@ -2563,14 +2570,14 @@
       <c r="B41" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E41" s="3">
-        <v>40</v>
+      <c r="E41" s="1">
+        <v>11.1</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>70</v>
@@ -2583,14 +2590,14 @@
       <c r="B42" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="E42" s="3">
-        <v>41</v>
+      <c r="E42" s="1">
+        <v>11.1</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>70</v>
@@ -2603,14 +2610,14 @@
       <c r="B43" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D43" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E43" s="3">
-        <v>42</v>
+      <c r="E43" s="1">
+        <v>11.1</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>70</v>
@@ -2623,14 +2630,14 @@
       <c r="B44" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D44" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="E44" s="3">
-        <v>43</v>
+      <c r="E44" s="1">
+        <v>2.2200000000000002</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>117</v>
@@ -2643,14 +2650,14 @@
       <c r="B45" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D45" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="E45" s="3">
-        <v>44</v>
+      <c r="E45" s="1">
+        <v>2.2200000000000002</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>117</v>
@@ -2663,14 +2670,14 @@
       <c r="B46" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D46" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E46" s="3">
-        <v>45</v>
+      <c r="E46" s="1">
+        <v>0.53</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>117</v>
@@ -2683,14 +2690,14 @@
       <c r="B47" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="E47" s="3">
-        <v>46</v>
+      <c r="E47" s="1">
+        <v>0.53</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>117</v>
@@ -2703,14 +2710,14 @@
       <c r="B48" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E48" s="3">
-        <v>47</v>
+      <c r="E48" s="1">
+        <v>1.5</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>128</v>
@@ -2723,14 +2730,14 @@
       <c r="B49" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D49" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E49" s="3">
-        <v>48</v>
+      <c r="E49" s="1">
+        <v>1.5</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>128</v>
@@ -2743,14 +2750,14 @@
       <c r="B50" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="E50" s="3">
-        <v>49</v>
+      <c r="E50" s="1">
+        <v>1.5</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>128</v>
@@ -2763,14 +2770,14 @@
       <c r="B51" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D51" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E51" s="3">
-        <v>50</v>
+      <c r="E51" s="1">
+        <v>1.5</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>128</v>
@@ -2783,14 +2790,14 @@
       <c r="B52" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D52" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E52" s="3">
-        <v>51</v>
+      <c r="E52" s="1">
+        <v>11</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>141</v>
@@ -2803,14 +2810,14 @@
       <c r="B53" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D53" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E53" s="3">
-        <v>52</v>
+      <c r="E53" s="1">
+        <v>11</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>141</v>
@@ -2823,14 +2830,14 @@
       <c r="B54" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D54" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="E54" s="3">
-        <v>53</v>
+      <c r="E54" s="1">
+        <v>11</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>141</v>
@@ -2843,14 +2850,14 @@
       <c r="B55" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D55" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E55" s="3">
-        <v>54</v>
+      <c r="E55" s="1">
+        <v>11</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>141</v>
@@ -2863,14 +2870,14 @@
       <c r="B56" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D56" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E56" s="3">
-        <v>55</v>
+      <c r="E56" s="1">
+        <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>70</v>
@@ -2883,14 +2890,14 @@
       <c r="B57" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D57" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E57" s="3">
-        <v>56</v>
+      <c r="E57" s="1">
+        <v>30</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>70</v>
@@ -2903,14 +2910,14 @@
       <c r="B58" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="E58" s="3">
-        <v>57</v>
+      <c r="E58" s="1">
+        <v>30</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>70</v>
@@ -2923,14 +2930,14 @@
       <c r="B59" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D59" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="E59" s="3">
-        <v>58</v>
+      <c r="E59" s="1">
+        <v>30</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>70</v>
@@ -2943,14 +2950,14 @@
       <c r="B60" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E60" s="3">
-        <v>59</v>
+      <c r="E60" s="1">
+        <v>30</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>70</v>
@@ -2963,14 +2970,14 @@
       <c r="B61" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D61" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="E61" s="3">
-        <v>60</v>
+      <c r="E61" s="1">
+        <v>30</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>70</v>
@@ -2983,14 +2990,14 @@
       <c r="B62" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="E62" s="3">
-        <v>61</v>
+      <c r="E62" s="1">
+        <v>30</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>70</v>
@@ -3003,14 +3010,14 @@
       <c r="B63" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D63" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="E63" s="3">
-        <v>62</v>
+      <c r="E63" s="1">
+        <v>30</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>70</v>
@@ -3023,14 +3030,14 @@
       <c r="B64" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D64" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E64" s="3">
-        <v>63</v>
+      <c r="E64" s="1">
+        <v>30</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>70</v>
@@ -3043,14 +3050,14 @@
       <c r="B65" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D65" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="E65" s="3">
-        <v>64</v>
+      <c r="E65" s="1">
+        <v>30</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>70</v>
@@ -3063,14 +3070,14 @@
       <c r="B66" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="E66" s="3">
-        <v>65</v>
+      <c r="E66" s="1">
+        <v>30</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>70</v>
@@ -3083,14 +3090,14 @@
       <c r="B67" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D67" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E67" s="3">
-        <v>66</v>
+      <c r="E67" s="1">
+        <v>30</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>70</v>
@@ -3103,14 +3110,14 @@
       <c r="B68" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="E68" s="3">
-        <v>67</v>
+      <c r="E68" s="1">
+        <v>6</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>4</v>
@@ -3123,14 +3130,14 @@
       <c r="B69" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D69" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E69" s="3">
-        <v>68</v>
+      <c r="E69" s="1">
+        <v>6</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>4</v>
@@ -3143,14 +3150,14 @@
       <c r="B70" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="E70" s="3">
-        <v>69</v>
+      <c r="E70" s="1">
+        <v>6</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>70</v>
@@ -3163,14 +3170,14 @@
       <c r="B71" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D71" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="E71" s="3">
-        <v>70</v>
+      <c r="E71" s="1">
+        <v>6</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>4</v>
@@ -3183,14 +3190,14 @@
       <c r="B72" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="E72" s="3">
-        <v>71</v>
+      <c r="E72" s="1">
+        <v>6</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>4</v>
@@ -3203,14 +3210,14 @@
       <c r="B73" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D73" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E73" s="3">
-        <v>72</v>
+      <c r="E73" s="1">
+        <v>6</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>70</v>
@@ -3223,14 +3230,14 @@
       <c r="B74" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D74" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="E74" s="3">
-        <v>73</v>
+      <c r="E74" s="1">
+        <v>9.1999999999999993</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>4</v>
@@ -3243,14 +3250,14 @@
       <c r="B75" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D75" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E75" s="3">
-        <v>74</v>
+      <c r="E75" s="1">
+        <v>9.1999999999999993</v>
       </c>
       <c r="F75" s="3" t="str">
         <f>$F$65</f>
@@ -3264,14 +3271,14 @@
       <c r="B76" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E76" s="3">
-        <v>75</v>
+      <c r="E76" s="1">
+        <v>9.1999999999999993</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>4</v>
@@ -3284,14 +3291,14 @@
       <c r="B77" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E77" s="3">
-        <v>76</v>
+      <c r="E77" s="1">
+        <v>1.5</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>4</v>
@@ -3304,14 +3311,14 @@
       <c r="B78" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E78" s="3">
-        <v>77</v>
+      <c r="E78" s="1">
+        <v>5</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>4</v>
@@ -3324,14 +3331,14 @@
       <c r="B79" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E79" s="3">
-        <v>78</v>
+      <c r="E79" s="1">
+        <v>5</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>4</v>
@@ -3344,14 +3351,14 @@
       <c r="B80" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E80" s="3">
-        <v>79</v>
+      <c r="E80" s="1">
+        <v>10</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>4</v>
@@ -3364,14 +3371,14 @@
       <c r="B81" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D81" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E81" s="3">
-        <v>80</v>
+      <c r="E81" s="1">
+        <v>30</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>4</v>
@@ -3384,14 +3391,14 @@
       <c r="B82" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="E82" s="3">
-        <v>81</v>
+      <c r="E82" s="1">
+        <v>1.5</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>4</v>
@@ -3404,14 +3411,14 @@
       <c r="B83" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D83" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E83" s="3">
-        <v>82</v>
+      <c r="E83" s="1">
+        <v>10</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>4</v>
@@ -3424,14 +3431,14 @@
       <c r="B84" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E84" s="3">
-        <v>83</v>
+      <c r="E84" s="1">
+        <v>30</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>4</v>
@@ -3444,14 +3451,14 @@
       <c r="B85" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D85" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E85" s="3">
-        <v>84</v>
+      <c r="E85" s="1">
+        <v>5.6</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>229</v>
@@ -3464,14 +3471,14 @@
       <c r="B86" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D86" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E86" s="3">
-        <v>85</v>
+      <c r="E86" s="1">
+        <v>35</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>4</v>
@@ -3484,14 +3491,14 @@
       <c r="B87" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D87" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="E87" s="3">
-        <v>86</v>
+      <c r="E87" s="1">
+        <v>100</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>4</v>
@@ -3504,14 +3511,14 @@
       <c r="B88" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D88" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E88" s="3">
-        <v>87</v>
+      <c r="E88" s="1">
+        <v>5</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>229</v>
@@ -3524,14 +3531,14 @@
       <c r="B89" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D89" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E89" s="3">
-        <v>88</v>
+      <c r="E89" s="1">
+        <v>5</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>229</v>
@@ -3544,14 +3551,14 @@
       <c r="B90" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D90" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E90" s="3">
-        <v>89</v>
+      <c r="E90" s="1">
+        <v>11</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>229</v>
@@ -3564,14 +3571,14 @@
       <c r="B91" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D91" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E91" s="3">
-        <v>90</v>
+      <c r="E91" s="1">
+        <v>11</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>229</v>
@@ -3584,14 +3591,14 @@
       <c r="B92" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D92" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E92" s="3">
-        <v>91</v>
+      <c r="E92" s="1">
+        <v>111</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>244</v>
@@ -3604,14 +3611,14 @@
       <c r="B93" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D93" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="E93" s="3">
-        <v>92</v>
+      <c r="E93" s="1">
+        <v>190</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>4</v>
@@ -3624,14 +3631,14 @@
       <c r="B94" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D94" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E94" s="3">
-        <v>93</v>
+      <c r="E94" s="1">
+        <v>30</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>4</v>
@@ -3644,14 +3651,14 @@
       <c r="B95" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D95" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="E95" s="3">
-        <v>94</v>
+      <c r="E95" s="1">
+        <v>30</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>4</v>
@@ -3664,14 +3671,14 @@
       <c r="B96" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C96" s="1" t="s">
+      <c r="C96" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D96" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E96" s="3">
-        <v>95</v>
+      <c r="E96" s="1">
+        <v>10</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>4</v>
@@ -3684,14 +3691,14 @@
       <c r="B97" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C97" s="1" t="s">
+      <c r="C97" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D97" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E97" s="3">
-        <v>96</v>
+      <c r="E97" s="1">
+        <v>10</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>4</v>
@@ -3704,14 +3711,14 @@
       <c r="B98" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C98" s="1" t="s">
+      <c r="C98" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D98" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E98" s="3">
-        <v>97</v>
+      <c r="E98" s="1">
+        <v>10</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>4</v>
@@ -3724,14 +3731,14 @@
       <c r="B99" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="C99" s="1" t="s">
+      <c r="C99" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D99" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="E99" s="3">
-        <v>98</v>
+      <c r="E99" s="1">
+        <v>5</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>4</v>
@@ -3744,14 +3751,14 @@
       <c r="B100" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C100" s="1" t="s">
+      <c r="C100" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D100" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E100" s="3">
-        <v>99</v>
+      <c r="E100" s="1">
+        <v>11</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>229</v>
@@ -3764,14 +3771,14 @@
       <c r="B101" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C101" s="1" t="s">
+      <c r="C101" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D101" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="E101" s="3">
-        <v>100</v>
+      <c r="E101" s="1">
+        <v>11</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>229</v>
@@ -3784,14 +3791,14 @@
       <c r="B102" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C102" s="1" t="s">
+      <c r="C102" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D102" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="E102" s="3">
-        <v>101</v>
+      <c r="E102" s="1">
+        <v>5</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>229</v>
@@ -3804,14 +3811,14 @@
       <c r="B103" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C103" s="1" t="s">
+      <c r="C103" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D103" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E103" s="3">
-        <v>102</v>
+      <c r="E103" s="1">
+        <v>5</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>229</v>
@@ -3824,14 +3831,14 @@
       <c r="B104" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C104" s="1" t="s">
+      <c r="C104" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D104" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="E104" s="3">
-        <v>103</v>
+      <c r="E104" s="1">
+        <v>2</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>229</v>
@@ -3844,14 +3851,14 @@
       <c r="B105" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="C105" s="1" t="s">
+      <c r="C105" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D105" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="E105" s="3">
-        <v>104</v>
+      <c r="E105" s="1">
+        <v>111</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>244</v>
@@ -3864,14 +3871,14 @@
       <c r="B106" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="C106" s="1" t="s">
+      <c r="C106" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D106" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="E106" s="3">
-        <v>105</v>
+      <c r="E106" s="1">
+        <v>6</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>4</v>
@@ -3884,14 +3891,14 @@
       <c r="B107" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C107" s="1" t="s">
+      <c r="C107" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D107" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="E107" s="3">
-        <v>106</v>
+      <c r="E107" s="1">
+        <v>1.5</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>4</v>
@@ -3904,14 +3911,14 @@
       <c r="B108" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D108" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="E108" s="3">
-        <v>107</v>
+      <c r="E108" s="1">
+        <v>0.75</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>278</v>
@@ -3924,14 +3931,14 @@
       <c r="B109" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C109" s="1" t="s">
+      <c r="C109" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D109" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E109" s="3">
-        <v>108</v>
+      <c r="E109" s="1">
+        <v>0.4</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>278</v>
@@ -3944,14 +3951,14 @@
       <c r="B110" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="C110" s="1" t="s">
+      <c r="C110" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D110" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="E110" s="3">
-        <v>109</v>
+      <c r="E110" s="1">
+        <v>0.4</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>278</v>
@@ -3964,14 +3971,14 @@
       <c r="B111" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="C111" s="1" t="s">
+      <c r="C111" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D111" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="E111" s="3">
-        <v>110</v>
+      <c r="E111" s="1">
+        <v>0.75</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>278</v>
@@ -3984,14 +3991,14 @@
       <c r="B112" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="C112" s="1" t="s">
+      <c r="C112" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D112" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="E112" s="3">
-        <v>111</v>
+      <c r="E112" s="1">
+        <v>0.4</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>278</v>
@@ -4004,14 +4011,14 @@
       <c r="B113" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="C113" s="1" t="s">
+      <c r="C113" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D113" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E113" s="3">
-        <v>112</v>
+      <c r="E113" s="1">
+        <v>0.4</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>278</v>
@@ -4024,14 +4031,14 @@
       <c r="B114" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="C114" s="1" t="s">
+      <c r="C114" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D114" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="E114" s="3">
-        <v>113</v>
+      <c r="E114" s="1">
+        <v>0.75</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>278</v>
@@ -4044,14 +4051,14 @@
       <c r="B115" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D115" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="E115" s="3">
-        <v>114</v>
+      <c r="E115" s="1">
+        <v>0.4</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>278</v>
@@ -4064,14 +4071,14 @@
       <c r="B116" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="C116" s="1" t="s">
+      <c r="C116" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D116" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="E116" s="3">
-        <v>115</v>
+      <c r="E116" s="1">
+        <v>0.4</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>278</v>
@@ -4084,14 +4091,14 @@
       <c r="B117" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="C117" s="1" t="s">
+      <c r="C117" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D117" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="E117" s="3">
-        <v>116</v>
+      <c r="E117" s="1">
+        <v>0.4</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>278</v>
@@ -4104,14 +4111,14 @@
       <c r="B118" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="C118" s="1" t="s">
+      <c r="C118" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D118" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="E118" s="3">
-        <v>117</v>
+      <c r="E118" s="1">
+        <v>2</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>229</v>
@@ -4124,14 +4131,14 @@
       <c r="B119" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C119" s="1" t="s">
+      <c r="C119" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D119" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="E119" s="3">
-        <v>118</v>
+      <c r="E119" s="1">
+        <v>0.4</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>278</v>
@@ -4144,14 +4151,14 @@
       <c r="B120" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="C120" s="1" t="s">
+      <c r="C120" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D120" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="E120" s="3">
-        <v>119</v>
+      <c r="E120" s="1">
+        <v>45</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>4</v>
@@ -4164,14 +4171,14 @@
       <c r="B121" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D121" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E121" s="3">
-        <v>120</v>
+      <c r="E121" s="1">
+        <v>45</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>4</v>
@@ -4184,14 +4191,14 @@
       <c r="B122" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="C122" s="1" t="s">
+      <c r="C122" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D122" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="E122" s="3">
-        <v>121</v>
+      <c r="E122" s="1">
+        <v>45</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>4</v>
@@ -4204,14 +4211,14 @@
       <c r="B123" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="C123" s="1" t="s">
+      <c r="C123" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D123" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="E123" s="3">
-        <v>122</v>
+      <c r="E123" s="1">
+        <v>191</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>4</v>
@@ -4224,14 +4231,14 @@
       <c r="B124" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="C124" s="1" t="s">
+      <c r="C124" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D124" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="E124" s="3">
-        <v>123</v>
+      <c r="E124" s="1">
+        <v>75</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>327</v>
@@ -4244,14 +4251,14 @@
       <c r="B125" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C125" s="1" t="s">
+      <c r="C125" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D125" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="E125" s="3">
-        <v>124</v>
+      <c r="E125" s="1">
+        <v>11</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>331</v>
@@ -4264,14 +4271,14 @@
       <c r="B126" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C126" s="1" t="s">
+      <c r="C126" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D126" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="E126" s="3">
-        <v>125</v>
+      <c r="E126" s="1">
+        <v>11</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>331</v>
@@ -4284,14 +4291,14 @@
       <c r="B127" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C127" s="1" t="s">
+      <c r="C127" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D127" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="E127" s="3">
-        <v>126</v>
+      <c r="E127" s="1">
+        <v>1.5</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>4</v>
@@ -4304,14 +4311,14 @@
       <c r="B128" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C128" s="1" t="s">
+      <c r="C128" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D128" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E128" s="3">
-        <v>127</v>
+      <c r="E128" s="1">
+        <v>7.5</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>331</v>
@@ -4324,14 +4331,14 @@
       <c r="B129" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C129" s="1" t="s">
+      <c r="C129" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D129" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="E129" s="3">
-        <v>128</v>
+      <c r="E129" s="1">
+        <v>7.5</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>331</v>
@@ -4344,14 +4351,14 @@
       <c r="B130" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C130" s="1" t="s">
+      <c r="C130" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D130" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E130" s="3">
-        <v>129</v>
+      <c r="E130" s="1">
+        <v>11</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>331</v>
@@ -4364,14 +4371,14 @@
       <c r="B131" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C131" s="1" t="s">
+      <c r="C131" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D131" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E131" s="3">
-        <v>130</v>
+      <c r="E131" s="1">
+        <v>11</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>331</v>
@@ -4384,14 +4391,14 @@
       <c r="B132" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C132" s="1" t="s">
+      <c r="C132" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D132" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="E132" s="3">
-        <v>131</v>
+      <c r="E132" s="1">
+        <v>1.5</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>4</v>
@@ -4404,14 +4411,14 @@
       <c r="B133" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C133" s="1" t="s">
+      <c r="C133" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D133" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="E133" s="3">
-        <v>132</v>
+      <c r="E133" s="1">
+        <v>7.5</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>331</v>
@@ -4424,14 +4431,14 @@
       <c r="B134" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="C134" s="1" t="s">
+      <c r="C134" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D134" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E134" s="3">
-        <v>133</v>
+      <c r="E134" s="1">
+        <v>7.5</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>331</v>
@@ -4444,14 +4451,14 @@
       <c r="B135" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="C135" s="1" t="s">
+      <c r="C135" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D135" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="E135" s="3">
-        <v>134</v>
+      <c r="E135" s="1">
+        <v>11</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>331</v>
@@ -4464,14 +4471,14 @@
       <c r="B136" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="C136" s="1" t="s">
+      <c r="C136" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D136" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="E136" s="3">
-        <v>135</v>
+      <c r="E136" s="1">
+        <v>11</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>331</v>
@@ -4484,14 +4491,14 @@
       <c r="B137" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="C137" s="1" t="s">
+      <c r="C137" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D137" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="E137" s="3">
-        <v>136</v>
+      <c r="E137" s="1">
+        <v>1.5</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>4</v>
@@ -4504,14 +4511,14 @@
       <c r="B138" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="C138" s="1" t="s">
+      <c r="C138" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="E138" s="3">
-        <v>137</v>
+      <c r="E138" s="1">
+        <v>7.5</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>331</v>
@@ -4524,14 +4531,14 @@
       <c r="B139" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="C139" s="1" t="s">
+      <c r="C139" s="6" t="s">
         <v>2</v>
       </c>
       <c r="D139" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="E139" s="3">
-        <v>138</v>
+      <c r="E139" s="1">
+        <v>7.5</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>331</v>
@@ -5098,6 +5105,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.59055118110236227" top="0.59055118110236227" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="77" orientation="landscape" r:id="rId1"/>
 </worksheet>
